--- a/studentdemo.xlsx
+++ b/studentdemo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CPF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CPF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C62F432-644B-4DDF-8679-EF12EAFB5DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B11B97A-9952-4EA7-A1DC-AF5DDEBDC02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{49476ED0-3312-43B0-8A31-2E2DD8A26157}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{49476ED0-3312-43B0-8A31-2E2DD8A26157}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="68">
   <si>
     <t>rollnumber</t>
   </si>
@@ -51,10 +51,193 @@
     <t/>
   </si>
   <si>
-    <t>22ITR035</t>
+    <t>22ITF001</t>
   </si>
   <si>
-    <t>Immanu</t>
+    <t>Dr.S.Varadhaganapathy</t>
+  </si>
+  <si>
+    <t>Faculty</t>
+  </si>
+  <si>
+    <t>22ITF002</t>
+  </si>
+  <si>
+    <t>Dr.J.Premalatha</t>
+  </si>
+  <si>
+    <t>22ITF003</t>
+  </si>
+  <si>
+    <t>Dr.S.Anandamurugan</t>
+  </si>
+  <si>
+    <t>22ITF004</t>
+  </si>
+  <si>
+    <t>Dr.T.Abirami</t>
+  </si>
+  <si>
+    <t>22ITF005</t>
+  </si>
+  <si>
+    <t>Dr.G.K.Kamalam</t>
+  </si>
+  <si>
+    <t>22ITF006</t>
+  </si>
+  <si>
+    <t>Dr.R.Shanthakumari</t>
+  </si>
+  <si>
+    <t>22ITF007</t>
+  </si>
+  <si>
+    <t>Dr.E.M.Roopa Devi</t>
+  </si>
+  <si>
+    <t>22ITF008</t>
+  </si>
+  <si>
+    <t>D.Vijay Anand</t>
+  </si>
+  <si>
+    <t>22ITF009</t>
+  </si>
+  <si>
+    <t>A.P.Ponselvakumar</t>
+  </si>
+  <si>
+    <t>22ITF010</t>
+  </si>
+  <si>
+    <t>A.Jeevanantham</t>
+  </si>
+  <si>
+    <t>22ITF011</t>
+  </si>
+  <si>
+    <t>S.Vinothkumar</t>
+  </si>
+  <si>
+    <t>22ITF012</t>
+  </si>
+  <si>
+    <t>Dr.V.Devisurya</t>
+  </si>
+  <si>
+    <t>22ITF013</t>
+  </si>
+  <si>
+    <t>R.Aarthi</t>
+  </si>
+  <si>
+    <t>22ITF014</t>
+  </si>
+  <si>
+    <t>S.Sujitha</t>
+  </si>
+  <si>
+    <t>22ITF015</t>
+  </si>
+  <si>
+    <t>K.Sruthi</t>
+  </si>
+  <si>
+    <t>22ITF016</t>
+  </si>
+  <si>
+    <t>S.Kavithra</t>
+  </si>
+  <si>
+    <t>22ITF017</t>
+  </si>
+  <si>
+    <t>R.Sandhiya</t>
+  </si>
+  <si>
+    <t>22ITF018</t>
+  </si>
+  <si>
+    <t>V.P.Gayathri</t>
+  </si>
+  <si>
+    <t>22ITF019</t>
+  </si>
+  <si>
+    <t>P.Vanitha</t>
+  </si>
+  <si>
+    <t>22ITF020</t>
+  </si>
+  <si>
+    <t>A.Deenu Mol</t>
+  </si>
+  <si>
+    <t>22ITF021</t>
+  </si>
+  <si>
+    <t>T.Vaishnavi</t>
+  </si>
+  <si>
+    <t>22ITF022</t>
+  </si>
+  <si>
+    <t>S.Krishnaveni</t>
+  </si>
+  <si>
+    <t>22ITF023</t>
+  </si>
+  <si>
+    <t>M.E.Prathika</t>
+  </si>
+  <si>
+    <t>22ITF024</t>
+  </si>
+  <si>
+    <t>T.S.Vishnu Priya</t>
+  </si>
+  <si>
+    <t>22ITF025</t>
+  </si>
+  <si>
+    <t>Monica Murugesan</t>
+  </si>
+  <si>
+    <t>22ITF026</t>
+  </si>
+  <si>
+    <t>S.Suganya</t>
+  </si>
+  <si>
+    <t>22ITF027</t>
+  </si>
+  <si>
+    <t>G.Sasikala</t>
+  </si>
+  <si>
+    <t>22ITF028</t>
+  </si>
+  <si>
+    <t>E.Sowmiya</t>
+  </si>
+  <si>
+    <t>22ITF029</t>
+  </si>
+  <si>
+    <t>S.Sripriya</t>
+  </si>
+  <si>
+    <t>22ITF030</t>
+  </si>
+  <si>
+    <t>M.Nithyakumar</t>
+  </si>
+  <si>
+    <t>22ITF031</t>
+  </si>
+  <si>
+    <t>S.Govindaraj</t>
   </si>
 </sst>
 </file>
@@ -106,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -117,6 +300,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,139 +635,439 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="43.2">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
+      <c r="C2" s="5">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="28.8">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.2">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28.8">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="28.8">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.2">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.2">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28.8">
+      <c r="A9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="43.2">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="28.8">
+      <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.8">
+      <c r="A12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28.8">
+      <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="5">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="2"/>
+      <c r="A16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="5">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28.8">
+      <c r="A17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="5">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28.8">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="5">
+        <v>5</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="5">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="28.8">
+      <c r="A21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="5">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="28.8">
+      <c r="A22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="5">
+        <v>5</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28.8">
+      <c r="A23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="5">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="28.8">
+      <c r="A24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="5">
+        <v>5</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="28.8">
+      <c r="A25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="43.2">
+      <c r="A26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="5">
+        <v>5</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="28.8">
+      <c r="A27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="5">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.8">
+      <c r="A28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="5">
+        <v>5</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="28.8">
+      <c r="A29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="5">
+        <v>5</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="5">
+        <v>5</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="28.8">
+      <c r="A31" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="5">
+        <v>5</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="28.8">
+      <c r="A32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="5">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1"/>
